--- a/research/traditional_assets/database/data/kazakhstan/kazakhstan_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/kazakhstan/kazakhstan_investments_asset_management.xlsx
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="K2">
-        <v>-1.49</v>
+        <v>-1.34</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>159.3</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.146900269541779</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-118.8805970149254</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,58 +609,61 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>159.3</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.52</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V2">
-        <v>0.002302922940655447</v>
+        <v>0.0009433962264150943</v>
       </c>
       <c r="W2">
-        <v>-0.8764705882352941</v>
+        <v>1.616405307599518</v>
       </c>
       <c r="X2">
-        <v>0.09115449731022837</v>
+        <v>0.07792692622263711</v>
       </c>
       <c r="Y2">
-        <v>-0.9676250855455225</v>
+        <v>1.538478381376881</v>
       </c>
       <c r="AB2">
-        <v>0.09115449731022837</v>
+        <v>0.07681539467049031</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AG2">
-        <v>-0.52</v>
+        <v>3.34</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.04393763690246102</v>
       </c>
       <c r="AI2">
-        <v>-0</v>
+        <v>-1.306513409961686</v>
       </c>
       <c r="AJ2">
-        <v>-0.002308238636363636</v>
+        <v>0.0430745421717823</v>
       </c>
       <c r="AK2">
-        <v>0.385470719051149</v>
+        <v>-1.246268656716418</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.07</v>
+        <v>-3.44</v>
       </c>
       <c r="AQ2">
-        <v>2.411214953271028</v>
+        <v>1.383720930232558</v>
       </c>
     </row>
     <row r="3">
@@ -680,16 +683,16 @@
         </is>
       </c>
       <c r="K3">
-        <v>-1.49</v>
+        <v>-1.34</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>159.3</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>2.146900269541779</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-118.8805970149254</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -701,58 +704,61 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>159.3</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.52</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="V3">
-        <v>0.002302922940655447</v>
+        <v>0.0009433962264150943</v>
       </c>
       <c r="W3">
-        <v>-0.8764705882352941</v>
+        <v>1.616405307599518</v>
       </c>
       <c r="X3">
-        <v>0.09115449731022837</v>
+        <v>0.07792692622263711</v>
       </c>
       <c r="Y3">
-        <v>-0.9676250855455225</v>
+        <v>1.538478381376881</v>
       </c>
       <c r="AB3">
-        <v>0.09115449731022837</v>
+        <v>0.07681539467049031</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AG3">
-        <v>-0.52</v>
+        <v>3.34</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.04393763690246102</v>
       </c>
       <c r="AI3">
-        <v>-0</v>
+        <v>-1.306513409961686</v>
       </c>
       <c r="AJ3">
-        <v>-0.002308238636363636</v>
+        <v>0.0430745421717823</v>
       </c>
       <c r="AK3">
-        <v>0.385470719051149</v>
+        <v>-1.246268656716418</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.07</v>
+        <v>-3.44</v>
       </c>
       <c r="AQ3">
-        <v>2.411214953271028</v>
+        <v>1.383720930232558</v>
       </c>
     </row>
   </sheetData>
